--- a/Employee_Reports_wi52/Errolnil Purificacion Atienza Q0541.xlsx
+++ b/Employee_Reports_wi52/Errolnil Purificacion Atienza Q0541.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-255</v>
+        <v>-263</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1461,11 +1461,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-119</v>
+        <v>-127</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-63</v>
+        <v>-71</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-386</v>
+        <v>-394</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-162</v>
+        <v>-170</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-122</v>
+        <v>-130</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
@@ -1694,11 +1694,11 @@
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-162</v>
+        <v>-170</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
@@ -1743,11 +1743,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-120</v>
+        <v>-128</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
@@ -1792,11 +1792,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-121</v>
+        <v>-129</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
@@ -1841,11 +1841,11 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-22</v>
+        <v>-30</v>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
@@ -1890,11 +1890,11 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
@@ -1939,11 +1939,11 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-19</v>
+        <v>-27</v>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
@@ -1976,11 +1976,11 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
@@ -2025,11 +2025,11 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
@@ -2074,11 +2074,11 @@
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1</v>
+        <v>-9</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
@@ -2111,11 +2111,11 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
